--- a/logs/log_durations/log_durations.xlsx
+++ b/logs/log_durations/log_durations.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,34 @@
       <b val="1"/>
       <color rgb="00853D3D"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00872525"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B6B6B"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00767676"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00807D7D"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00585858"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00817373"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00737373"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -220,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,17 +257,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="9" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="11" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="19" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -609,10 +644,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -620,6 +655,10 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -663,6 +702,26 @@
           <t>Bible Change %</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Nasa Min</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Nasa Avg</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Nasa Max</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Nasa Change %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -691,6 +750,18 @@
       <c r="H2" s="7" t="n">
         <v>0.4190935390549663</v>
       </c>
+      <c r="I2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -716,8 +787,20 @@
       <c r="G3" s="5" t="n">
         <v>10930.06</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="9" t="n">
         <v>0.2890497826900514</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1390.14</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>4088.57</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>10930.09</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>0.3398217056641795</v>
       </c>
     </row>
     <row r="4">
@@ -744,8 +827,20 @@
       <c r="G4" s="5" t="n">
         <v>479.79</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="11" t="n">
         <v>-0.5507303077725612</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>207.35</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>251.14</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="L4" s="12" t="n">
+        <v>-0.05600874611050372</v>
       </c>
     </row>
     <row r="5">
@@ -772,8 +867,20 @@
       <c r="G5" s="5" t="n">
         <v>17384.16</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="13" t="n">
         <v>0.7171561584923803</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>3899.16</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>6138.8</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>7236.11</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>-0.02705497156643116</v>
       </c>
     </row>
     <row r="6">
@@ -800,8 +907,20 @@
       <c r="G6" s="5" t="n">
         <v>8864.809999999999</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="15" t="n">
         <v>-3.619938176197836</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2522.85</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>0.4794419725000836</v>
       </c>
     </row>
     <row r="7">
@@ -828,8 +947,20 @@
       <c r="G7" s="5" t="n">
         <v>1197.73</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="16" t="n">
         <v>0.6627830661199031</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>517.59</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>678.24</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1076.37</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>0.007492390540856948</v>
       </c>
     </row>
     <row r="8">
@@ -856,8 +987,20 @@
       <c r="G8" s="5" t="n">
         <v>66.31999999999999</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="18" t="n">
         <v>-0.01407506702412874</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>108.66</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>-0.05684071381361529</v>
       </c>
     </row>
     <row r="9">
@@ -884,7 +1027,19 @@
       <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -912,8 +1067,20 @@
       <c r="G10" s="5" t="n">
         <v>1391.43</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="19" t="n">
         <v>-0.06314659744668109</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>668.52</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1156.13</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>2223.36</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>-0.3571034498949421</v>
       </c>
     </row>
     <row r="11">
@@ -940,8 +1107,20 @@
       <c r="G11" s="5" t="n">
         <v>487.79</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="20" t="n">
         <v>0.0985838567471618</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>513.3</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>600.5599999999999</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>-0.1107504544274213</v>
       </c>
     </row>
     <row r="12">
@@ -968,7 +1147,19 @@
       <c r="G12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -996,7 +1187,19 @@
       <c r="G13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1024,8 +1227,20 @@
       <c r="G14" s="5" t="n">
         <v>929.02</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="22" t="n">
         <v>0.5446906337944428</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>373.09</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>437.63</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>602.3099999999999</v>
+      </c>
+      <c r="L14" s="23" t="n">
+        <v>0.04755375642030125</v>
       </c>
     </row>
     <row r="15">
@@ -1052,8 +1267,20 @@
       <c r="G15" s="5" t="n">
         <v>169.2</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="24" t="n">
         <v>0.3726364041510154</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>164.22</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <v>-0.03612746092957162</v>
       </c>
     </row>
     <row r="16">
@@ -1062,25 +1289,1757 @@
           <t>KochSnowflake4</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="19" t="n">
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>190.56</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="5" t="n">
         <v>246.88</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="5" t="n">
         <v>392.53</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>185.52</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>244.68</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>286.54</v>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>0.00891121192482173</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GlitchWarpTransformer</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Duotone</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SwirlWarpTransformer</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HalftoneTransformer</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RadialWarp</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FractalWarp</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ScreenArtMain</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>1313.02</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>10931.11</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FluidWarpTransformer</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>278.37</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>597.08</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FractalWarpTransformer</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MeltMorphTransformer</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ThreeDExtrusion</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Halftone</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Anamorphic</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Colormap</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Posterization</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DuotoneTransformer</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ThermalImagingTransformer</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MeltMorph</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RadialWarpTransformer</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>InvertRGBTransformer</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FisheyeTransformer</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>135.98</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>189.13</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PosterizationTransformer</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AnamorphicTransformer</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>63.27</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>184.28</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Watercolor</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DataMoshTransformer</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Fisheye</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TritoneTransformer</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>66.86</v>
+      </c>
+      <c r="L44" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WheelTransformer</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>255.59</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>622.83</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DataMosh</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Tritone</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FluidWarp</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FlipWilsonTransformer</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>68.12</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>159.86</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Xray</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ColormapTransformer</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Wheel</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SwirlWarp</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ThreeDExtrusionTransformer</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="L54" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GlitchWarp</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ThermalImaging</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FlipWilson</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WatercolorTransformer</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>148.48</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>231.01</v>
+      </c>
+      <c r="L58" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>XrayTransformer</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="26" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J59" s="27" t="n">
+        <v>71.54000000000001</v>
+      </c>
+      <c r="K59" s="27" t="n">
+        <v>241.31</v>
+      </c>
+      <c r="L59" s="29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/logs/log_durations/log_durations.xlsx
+++ b/logs/log_durations/log_durations.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t xml:space="preserve">Generator</t>
   </si>
@@ -40,61 +40,67 @@
     <t xml:space="preserve">03-nasa Change %</t>
   </si>
   <si>
+    <t xml:space="preserve">04-jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04-jpeg Change %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScreenArtMain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PeripheralDriftIllusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KochSnowflake1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KochSnowflake2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bubbles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KochSnowflake3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KochSnowflake4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lojong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoesGenerator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NasaMapGenerator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KochSnowflake</t>
+  </si>
+  <si>
     <t xml:space="preserve">04-main timer</t>
   </si>
   <si>
     <t xml:space="preserve">04-main timer Change %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cubes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScreenArtMain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PeripheralDriftIllusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KochSnowflake1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KochSnowflake2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bubbles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KochSnowflake3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KochSnowflake4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lojong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoesGenerator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NasaMapGenerator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nasa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KochSnowflake</t>
   </si>
 </sst>
 </file>
@@ -105,7 +111,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,7 +145,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF816D6D"/>
+      <color rgb="FF656565"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -155,7 +161,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF3D3D3D"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -179,7 +185,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF606060"/>
+      <color rgb="FF7C7C7C"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -203,7 +209,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF817070"/>
+      <color rgb="FF844A4A"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -227,14 +233,6 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF535353"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <color rgb="FF7E7E7E"/>
       <name val="Cambria"/>
       <family val="0"/>
@@ -267,7 +265,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF6B6B6B"/>
+      <color rgb="FF863434"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -283,7 +281,15 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF835B5B"/>
+      <color rgb="FF676767"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF737373"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -299,15 +305,79 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF7D7D7D"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF872828"/>
+      <color rgb="FF474747"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF825D5D"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF292929"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF5A5A5A"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF747474"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF5B5B5B"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF2F2F2F"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF835555"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF825F5F"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF835353"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -418,7 +488,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -531,19 +601,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -567,53 +673,53 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF8B0000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF737373"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF816C6C"/>
-      <rgbColor rgb="FF835B5B"/>
-      <rgbColor rgb="FF707070"/>
-      <rgbColor rgb="FF816D6D"/>
+      <rgbColor rgb="FF835353"/>
+      <rgbColor rgb="FF5B5B5B"/>
+      <rgbColor rgb="FF7A7A7A"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF7D7D7D"/>
+      <rgbColor rgb="FF7E7E7E"/>
       <rgbColor rgb="FF863636"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FF835858"/>
       <rgbColor rgb="FF816F6F"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF707070"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF835555"/>
       <rgbColor rgb="FF8A0A0A"/>
-      <rgbColor rgb="FF7A7A7A"/>
+      <rgbColor rgb="FF656565"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FF817070"/>
+      <rgbColor rgb="FF816A6A"/>
+      <rgbColor rgb="FF7C7C7C"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF6A6A6A"/>
+      <rgbColor rgb="FF676767"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF767676"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FF816A6A"/>
-      <rgbColor rgb="FF6B6B6B"/>
-      <rgbColor rgb="FF7E7E7E"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF767676"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF606060"/>
-      <rgbColor rgb="FF872828"/>
-      <rgbColor rgb="FF835858"/>
-      <rgbColor rgb="FF535353"/>
-      <rgbColor rgb="FF3D3D3D"/>
+      <rgbColor rgb="FF825D5D"/>
+      <rgbColor rgb="FF6A6A6A"/>
+      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF5A5A5A"/>
+      <rgbColor rgb="FF747474"/>
+      <rgbColor rgb="FF825F5F"/>
+      <rgbColor rgb="FF292929"/>
+      <rgbColor rgb="FF844A4A"/>
+      <rgbColor rgb="FF863434"/>
+      <rgbColor rgb="FF474747"/>
+      <rgbColor rgb="FF2F2F2F"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -799,16 +905,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
   </cols>
   <sheetData>
@@ -858,10 +964,10 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0.133333333333333</v>
+        <v>-0.166666666666667</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -884,10 +990,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>794</v>
+        <v>463</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>-0.718614718614719</v>
+        <v>-0.00216450216450217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -936,10 +1042,10 @@
         <v>-0.0444444444444445</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>-0.340425531914894</v>
+        <v>-0.0212765957446809</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -962,10 +1068,10 @@
         <v>0.00732064421669107</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>600</v>
+        <v>548</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0.115044247787611</v>
+        <v>0.191740412979351</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1040,10 +1146,10 @@
         <v>-0.0590717299578059</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>372</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>-0.48207171314741</v>
+        <v>286</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>-0.139442231075697</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1082,13 +1188,13 @@
       <c r="C11" s="5" t="n">
         <v>246</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <v>-0.00819672131147541</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>244</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.00813008130081301</v>
       </c>
       <c r="G11" s="5" t="n">
@@ -1108,20 +1214,20 @@
       <c r="C12" s="5" t="n">
         <v>459</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <v>-0.0551724137931035</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>437</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="21" t="n">
         <v>0.0479302832244009</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>533</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>-0.219679633867277</v>
+        <v>319</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>0.270022883295195</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1134,20 +1240,20 @@
       <c r="C13" s="5" t="n">
         <v>851</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="21" t="n">
         <v>0.172983479105928</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1156</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="23" t="n">
         <v>-0.358401880141011</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2755</v>
+        <v>1335</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-1.38321799307959</v>
+        <v>-0.15484429065744</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1170,10 +1276,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.26530612244898</v>
+        <v>-0.0816326530612245</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1196,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>6112</v>
+        <v>8113</v>
       </c>
       <c r="H15" s="27" t="n">
-        <v>-0.0225865818972729</v>
+        <v>-0.357369918019073</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1212,7 +1318,7 @@
       <c r="C16" s="5" t="n">
         <v>896</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="23" t="n">
         <v>-0.756862745098039</v>
       </c>
       <c r="E16" s="5" t="n">
@@ -1222,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>0.930803571428571</v>
+        <v>1624</v>
+      </c>
+      <c r="H16" s="23" t="n">
+        <v>-0.8125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1248,36 +1354,234 @@
         <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>2235</v>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>0.639108671080252</v>
+        <v>3365</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>0.456644598740514</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="30" t="n">
+      <c r="B18" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="29" t="n">
+        <v>309</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C22" s="31" t="n">
+        <v>0.257142857142857</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>794</v>
+      </c>
+      <c r="C23" s="32" t="n">
+        <v>-0.714902807775378</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>-0.3125</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>-0.0948905109489051</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>372</v>
+      </c>
+      <c r="C29" s="35" t="n">
+        <v>-0.300699300699301</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="C32" s="36" t="n">
+        <v>-0.670846394984326</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2755</v>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>-1.06367041198502</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C34" s="37" t="n">
+        <v>0.320754716981132</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>6112</v>
+      </c>
+      <c r="C35" s="38" t="n">
+        <v>0.246641193146801</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C36" s="21" t="n">
+        <v>0.961822660098522</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C37" s="39" t="n">
+        <v>0.335809806835067</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="29" t="n">
         <v>313</v>
       </c>
-      <c r="H18" s="31" t="n">
-        <v>0</v>
+      <c r="C38" s="40" t="n">
+        <v>-0.0129449838187702</v>
       </c>
     </row>
   </sheetData>

--- a/logs/log_durations/log_durations.xlsx
+++ b/logs/log_durations/log_durations.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="68">
+  <fonts count="75">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -292,6 +292,34 @@
     <font>
       <b val="1"/>
       <color rgb="00853A3A"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00826565"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003A3A3A"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00807777"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00222222"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F0F0F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002A2A2A"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00826464"/>
     </font>
   </fonts>
   <fills count="2">
@@ -440,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -507,18 +535,25 @@
     <xf numFmtId="10" fontId="53" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="56" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="62" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="68" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="69" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="55" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="63" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="56" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="70" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="71" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="64" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="72" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="57" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="65" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="73" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="58" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="66" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="59" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="67" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="74" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -893,7 +928,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
   </cols>
@@ -2020,6 +2055,16 @@
           <t>09-maps Change %</t>
         </is>
       </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>10-transformers 1</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>10-transformers 1 Change %</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2039,6 +2084,12 @@
       <c r="E42" s="64" t="n">
         <v>0.1428571428571428</v>
       </c>
+      <c r="F42" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2058,6 +2109,12 @@
       <c r="E43" s="65" t="n">
         <v>0.008620689655172414</v>
       </c>
+      <c r="F43" s="5" t="n">
+        <v>541</v>
+      </c>
+      <c r="G43" s="66" t="n">
+        <v>-0.1760869565217391</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2077,6 +2134,12 @@
       <c r="E44" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2096,6 +2159,12 @@
       <c r="E45" s="23" t="n">
         <v>-0.5185185185185185</v>
       </c>
+      <c r="F45" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G45" s="21" t="n">
+        <v>0.3658536585365854</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2112,8 +2181,14 @@
       <c r="D46" s="5" t="n">
         <v>577</v>
       </c>
-      <c r="E46" s="66" t="n">
+      <c r="E46" s="67" t="n">
         <v>-0.2462203023758099</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>534</v>
+      </c>
+      <c r="G46" s="68" t="n">
+        <v>0.07452339688041594</v>
       </c>
     </row>
     <row r="47">
@@ -2134,6 +2209,12 @@
       <c r="E47" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2153,6 +2234,12 @@
       <c r="E48" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2163,7 +2250,7 @@
       <c r="B49" s="5" t="n">
         <v>216</v>
       </c>
-      <c r="C49" s="67" t="n">
+      <c r="C49" s="69" t="n">
         <v>0.009174311926605505</v>
       </c>
       <c r="D49" s="5" t="n">
@@ -2172,6 +2259,12 @@
       <c r="E49" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="F49" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="G49" s="70" t="n">
+        <v>-0.2731481481481481</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2191,6 +2284,12 @@
       <c r="E50" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2210,6 +2309,12 @@
       <c r="E51" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2220,7 +2325,7 @@
       <c r="B52" s="5" t="n">
         <v>327</v>
       </c>
-      <c r="C52" s="68" t="n">
+      <c r="C52" s="71" t="n">
         <v>-0.06862745098039216</v>
       </c>
       <c r="D52" s="5" t="n">
@@ -2229,6 +2334,12 @@
       <c r="E52" s="42" t="n">
         <v>-0.1498470948012232</v>
       </c>
+      <c r="F52" s="5" t="n">
+        <v>347</v>
+      </c>
+      <c r="G52" s="68" t="n">
+        <v>0.07712765957446809</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2245,8 +2356,14 @@
       <c r="D53" s="5" t="n">
         <v>782</v>
       </c>
-      <c r="E53" s="69" t="n">
+      <c r="E53" s="72" t="n">
         <v>-0.225705329153605</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>763</v>
+      </c>
+      <c r="G53" s="73" t="n">
+        <v>0.02429667519181586</v>
       </c>
     </row>
     <row r="54">
@@ -2258,7 +2375,7 @@
       <c r="B54" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="C54" s="70" t="n">
+      <c r="C54" s="66" t="n">
         <v>-0.09333333333333334</v>
       </c>
       <c r="D54" s="5" t="n">
@@ -2267,6 +2384,12 @@
       <c r="E54" s="21" t="n">
         <v>0.1951219512195122</v>
       </c>
+      <c r="F54" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="G54" s="74" t="n">
+        <v>-0.3636363636363636</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2283,8 +2406,14 @@
       <c r="D55" s="5" t="n">
         <v>4992</v>
       </c>
-      <c r="E55" s="71" t="n">
+      <c r="E55" s="75" t="n">
         <v>0.07743485492515247</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>7195</v>
+      </c>
+      <c r="G55" s="76" t="n">
+        <v>-0.4413060897435898</v>
       </c>
     </row>
     <row r="56">
@@ -2296,14 +2425,20 @@
       <c r="B56" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="C56" s="72" t="n">
+      <c r="C56" s="77" t="n">
         <v>0.02777777777777778</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="E56" s="73" t="n">
+      <c r="E56" s="78" t="n">
         <v>-0.02857142857142857</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="G56" s="79" t="n">
+        <v>-0.3333333333333333</v>
       </c>
     </row>
     <row r="57">
@@ -2315,14 +2450,20 @@
       <c r="B57" s="5" t="n">
         <v>929</v>
       </c>
-      <c r="C57" s="74" t="n">
+      <c r="C57" s="80" t="n">
         <v>0.01484623541887593</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>830</v>
       </c>
-      <c r="E57" s="75" t="n">
+      <c r="E57" s="81" t="n">
         <v>0.1065662002152852</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>825</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <v>0.006024096385542169</v>
       </c>
     </row>
     <row r="58">
@@ -2334,14 +2475,20 @@
       <c r="B58" s="29" t="n">
         <v>340</v>
       </c>
-      <c r="C58" s="76" t="n">
+      <c r="C58" s="82" t="n">
         <v>-0.1184210526315789</v>
       </c>
       <c r="D58" s="29" t="n">
         <v>304</v>
       </c>
-      <c r="E58" s="77" t="n">
+      <c r="E58" s="83" t="n">
         <v>0.1058823529411765</v>
+      </c>
+      <c r="F58" s="29" t="n">
+        <v>280</v>
+      </c>
+      <c r="G58" s="84" t="n">
+        <v>0.07894736842105263</v>
       </c>
     </row>
   </sheetData>
